--- a/.codex-work/outbound/writer-test.xlsx
+++ b/.codex-work/outbound/writer-test.xlsx
@@ -12,15 +12,21 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <name val="等线"/>
+      <b/>
+      <sz val="14"/>
+      <name val="I.Ming"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="等线"/>
+      <name val="I.Ming"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="字魂瘦金体"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,16 +64,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -80,15 +94,15 @@
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15.6" customWidth="1"/>
+    <col min="3" max="3" width="22.599999999999998" customWidth="1"/>
+    <col min="4" max="4" width="14.2" customWidth="1"/>
+    <col min="5" max="5" width="18.4" customWidth="1"/>
+    <col min="6" max="6" width="14.2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>编号</t>
@@ -104,12 +118,12 @@
           <t>SKU</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>处理方式</t>
         </is>
@@ -120,7 +134,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -134,12 +148,12 @@
           <t>P-TEST-SKU-001</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>调拨入库</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>检测通过</t>
         </is>
@@ -148,39 +162,39 @@
         <v>46259.4375</v>
       </c>
     </row>
-    <row r="5">
-      <c r="D5" s="0" t="inlineStr">
+    <row r="5" ht="28" customHeight="1">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>库位：</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="D6" s="0" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>签章：</t>
         </is>
       </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="D7" s="0" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>日期：</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>Aug 25 2026</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Sep 12 2026</t>
         </is>
       </c>
     </row>
